--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A467F241-0AB7-442E-9D44-C6AE6400D8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA466E5-1271-41EE-97BE-6B27642F9BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
@@ -34,9 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
+  </si>
+  <si>
+    <t>Q.2: Calculate Average Unit Price</t>
+  </si>
+  <si>
+    <t>Q.3: Count Total Sales Transactions</t>
   </si>
 </sst>
 </file>
@@ -388,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0599B9-E571-4B20-A5D2-127E923BB6B4}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -396,6 +402,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA466E5-1271-41EE-97BE-6B27642F9BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5534DF3B-0DB0-419D-8B78-BCF7C1993E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -43,6 +43,24 @@
   </si>
   <si>
     <t>Q.3: Count Total Sales Transactions</t>
+  </si>
+  <si>
+    <t>Q.4: Find the Highest and Lowest Unit Price</t>
+  </si>
+  <si>
+    <t>Q.5: Calculate Total Quantity Sold</t>
+  </si>
+  <si>
+    <t>Q.6: Count Unique Customers</t>
+  </si>
+  <si>
+    <t>Q.7: Count Missing Discount Values Using COUNTBLANK()</t>
+  </si>
+  <si>
+    <t>Q.8: Calculate Average Sales Amount Per Transaction Using AVERAGEX()</t>
+  </si>
+  <si>
+    <t>Q.9: Find the Highest and Lowest Sales Amount Using MAXX() and MINX()</t>
   </si>
 </sst>
 </file>
@@ -394,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0599B9-E571-4B20-A5D2-127E923BB6B4}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -412,6 +430,36 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5534DF3B-0DB0-419D-8B78-BCF7C1993E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE0649B-BD45-4F89-B36A-93393FA2E623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -61,6 +61,18 @@
   </si>
   <si>
     <t>Q.9: Find the Highest and Lowest Sales Amount Using MAXX() and MINX()</t>
+  </si>
+  <si>
+    <t>Q.10: Calculate the Product of Discount Multipliers Using PRODUCT()  and PRODUCTX()</t>
+  </si>
+  <si>
+    <t>Q.11: Count Non-Blank Product IDs Using COUNTA()</t>
+  </si>
+  <si>
+    <t>Q.12: Count Transactions with Quantity Greater Than 3 Using COUNTX()</t>
+  </si>
+  <si>
+    <t>Q.13: Calculate Total Discount Amount Using SUMX()</t>
   </si>
 </sst>
 </file>
@@ -412,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0599B9-E571-4B20-A5D2-127E923BB6B4}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -460,6 +472,26 @@
         <v>8</v>
       </c>
     </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE0649B-BD45-4F89-B36A-93393FA2E623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B647EF-4444-4755-9FFC-C9DED00619DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Beginner" sheetId="1" r:id="rId1"/>
+    <sheet name="Intermediate" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -73,6 +74,24 @@
   </si>
   <si>
     <t>Q.13: Calculate Total Discount Amount Using SUMX()</t>
+  </si>
+  <si>
+    <t>Q.14: Count Products Sold More then once Using DISTINCT COUNT()</t>
+  </si>
+  <si>
+    <t>Q.15: Calculate Net Sales Amount After Discount</t>
+  </si>
+  <si>
+    <t>Beginner Practice Questions</t>
+  </si>
+  <si>
+    <t>Intermediate Practice Questions</t>
+  </si>
+  <si>
+    <t>Q.1: Calculate Total Sales for the North Region Using CALCULATE()</t>
+  </si>
+  <si>
+    <t>Q.2: Calculate High-Value Sales Using FILTERS()</t>
   </si>
 </sst>
 </file>
@@ -424,72 +443,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0599B9-E571-4B20-A5D2-127E923BB6B4}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16DE348-3DD1-4281-9113-63A82C592DA5}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B647EF-4444-4755-9FFC-C9DED00619DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61048501-42E1-48F4-BE8C-2D9E474B1132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -92,6 +92,18 @@
   </si>
   <si>
     <t>Q.2: Calculate High-Value Sales Using FILTERS()</t>
+  </si>
+  <si>
+    <t>Q.3: Calculate Percentage Of Total Sales Using ALL()</t>
+  </si>
+  <si>
+    <t>Q.4: Calculate Regional Sales While Perserving Product Category Filter Using ALLEXCEPT()</t>
+  </si>
+  <si>
+    <t>Q.5: Calculate Visual Total Sales Using ALLSELECTED()</t>
+  </si>
+  <si>
+    <t>Q.6: Calculate Electronics Sales Using CALCULATE() and FILTER()</t>
   </si>
 </sst>
 </file>
@@ -533,7 +545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16DE348-3DD1-4281-9113-63A82C592DA5}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -551,6 +563,26 @@
         <v>18</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61048501-42E1-48F4-BE8C-2D9E474B1132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7551E6-58FF-45BF-9F0D-B266A3FEAE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -104,6 +104,21 @@
   </si>
   <si>
     <t>Q.6: Calculate Electronics Sales Using CALCULATE() and FILTER()</t>
+  </si>
+  <si>
+    <t>Q.7: Calculate Top Selling Product Sales Using SELECTEDVALUE()</t>
+  </si>
+  <si>
+    <t>Q.8: Retrieve Product Cost Price Using LOOKUPVALUE()(Not Done)</t>
+  </si>
+  <si>
+    <t>Q.9: Calculate Previous Transaction Sales Using OFFSET()(Not Done)</t>
+  </si>
+  <si>
+    <t>Q.10: Calculate Product Rank Using RANK()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q.11: Retrieve Sales Rank Within Each Region Using RANK () and PARTITIONBY() </t>
   </si>
 </sst>
 </file>
@@ -545,7 +560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16DE348-3DD1-4281-9113-63A82C592DA5}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -583,6 +598,31 @@
         <v>22</v>
       </c>
     </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7551E6-58FF-45BF-9F0D-B266A3FEAE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96BAD5C-8B9A-4E26-9881-C610646AFD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -119,6 +119,18 @@
   </si>
   <si>
     <t xml:space="preserve">Q.11: Retrieve Sales Rank Within Each Region Using RANK () and PARTITIONBY() </t>
+  </si>
+  <si>
+    <t>Q.12: Retrieve the Next Transaction Using INDEX()(Not Done)</t>
+  </si>
+  <si>
+    <t>Q.13: Retrieve Customer Sales Using RELATED()</t>
+  </si>
+  <si>
+    <t>Q.14: Calculate Total Sales for Each Cutomer Using RELATEDTABLE()</t>
+  </si>
+  <si>
+    <t>Q.15: Calculate Customer Lifetime (CLV) Using CALCULATE()</t>
   </si>
 </sst>
 </file>
@@ -560,7 +572,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16DE348-3DD1-4281-9113-63A82C592DA5}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -623,6 +635,26 @@
         <v>27</v>
       </c>
     </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\ReClasses\Power_BI\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96BAD5C-8B9A-4E26-9881-C610646AFD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944F4C8C-09F2-4D37-BB78-D7A5BE0C3703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{6D85762D-61CB-4066-BFD6-5FB565DD6CD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Beginner" sheetId="1" r:id="rId1"/>
     <sheet name="Intermediate" sheetId="2" r:id="rId2"/>
+    <sheet name="Advanced" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Q.1: Calculate Total Sales Amount</t>
   </si>
@@ -131,6 +132,21 @@
   </si>
   <si>
     <t>Q.15: Calculate Customer Lifetime (CLV) Using CALCULATE()</t>
+  </si>
+  <si>
+    <t>Advanced Practice Questions</t>
+  </si>
+  <si>
+    <t>Q.1: Calculate Year-to-Date (YTD) Sales Using CALCULATE() and DATESTYD()</t>
+  </si>
+  <si>
+    <t>Q.2: Calculate Month-to-Date (MTD) Sales Using CALCULATED() and DATESMTD()</t>
+  </si>
+  <si>
+    <t>Q.3: Calculate Quarter-to-Date (QTD) Sales Using CALCULATE() and DATESQTD()</t>
+  </si>
+  <si>
+    <t>Q.4: Calculate Previous Year Sales Using SAMEPERIOD-LAST YEAR()</t>
   </si>
 </sst>
 </file>
@@ -658,4 +674,39 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{957F8A97-C0C4-4373-B1D4-9DC47333A2C6}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>